--- a/datos.xlsx
+++ b/datos.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A4732AC-83C8-4FE2-AF62-06750DB5870C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14B993E1-523C-46E9-A464-4A4068BE5696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inventario_inicial" sheetId="1" r:id="rId1"/>
@@ -327,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="1"/>
@@ -349,6 +349,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1428,17 +1429,17 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0311D215-8F6F-415E-9314-F278B500F4CA}">
   <sheetPr>
-    <tabColor theme="9" tint="0.39997558519241921"/>
+    <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1448,8 +1449,16 @@
       <c r="C1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="E1" s="11">
+        <v>1.2</v>
+      </c>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1459,8 +1468,16 @@
       <c r="C2">
         <v>0.34</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2">
+        <f>0.9*C2</f>
+        <v>0.30600000000000005</v>
+      </c>
+      <c r="E2">
+        <f>1.2*C2</f>
+        <v>0.40800000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1470,8 +1487,16 @@
       <c r="C3">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3">
+        <f t="shared" ref="D3:D25" si="0">0.9*C3</f>
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="E3">
+        <f>1.2*C3</f>
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1481,8 +1506,16 @@
       <c r="C4">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="E4">
+        <f>1.2*C4</f>
+        <v>0.26400000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1492,8 +1525,16 @@
       <c r="C5">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="E5">
+        <f>1.2*C5</f>
+        <v>0.13200000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1</v>
       </c>
@@ -1503,8 +1544,15 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>1</v>
       </c>
@@ -1514,8 +1562,15 @@
       <c r="C7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1525,8 +1580,15 @@
       <c r="C8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1536,8 +1598,16 @@
       <c r="C9">
         <v>0.36</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="E9">
+        <f>1.2*C9</f>
+        <v>0.432</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1547,8 +1617,16 @@
       <c r="C10">
         <v>0.34</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0.30600000000000005</v>
+      </c>
+      <c r="E10">
+        <f>1.2*C10</f>
+        <v>0.40800000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1558,8 +1636,16 @@
       <c r="C11">
         <v>0.22</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="E11">
+        <f>1.2*C11</f>
+        <v>0.26400000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1569,8 +1655,16 @@
       <c r="C12">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.24300000000000002</v>
+      </c>
+      <c r="E12">
+        <f>1.2*C12</f>
+        <v>0.32400000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1580,8 +1674,16 @@
       <c r="C13">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="E13">
+        <f>1.2*C13</f>
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1591,8 +1693,15 @@
       <c r="C14">
         <v>0.84</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1602,8 +1711,15 @@
       <c r="C15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1613,8 +1729,15 @@
       <c r="C16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1624,8 +1747,16 @@
       <c r="C17">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="E17">
+        <f>1.2*C17</f>
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1635,8 +1766,16 @@
       <c r="C18">
         <v>0.34</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>0.30600000000000005</v>
+      </c>
+      <c r="E18">
+        <f>1.2*C18</f>
+        <v>0.40800000000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>3</v>
       </c>
@@ -1646,8 +1785,16 @@
       <c r="C19">
         <v>0.31</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>0.27900000000000003</v>
+      </c>
+      <c r="E19">
+        <f>1.2*C19</f>
+        <v>0.372</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>3</v>
       </c>
@@ -1657,8 +1804,16 @@
       <c r="C20">
         <v>0.38</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>0.34200000000000003</v>
+      </c>
+      <c r="E20">
+        <f>1.2*C20</f>
+        <v>0.45599999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>3</v>
       </c>
@@ -1668,8 +1823,16 @@
       <c r="C21">
         <v>0.19</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="E21">
+        <f>1.2*C21</f>
+        <v>0.22799999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>3</v>
       </c>
@@ -1679,8 +1842,16 @@
       <c r="C22">
         <v>0.59</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="E22">
+        <f>1.2*C22</f>
+        <v>0.70799999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>3</v>
       </c>
@@ -1690,8 +1861,15 @@
       <c r="C23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>3</v>
       </c>
@@ -1701,8 +1879,15 @@
       <c r="C24">
         <v>0.94</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>3</v>
       </c>
@@ -1711,6 +1896,14 @@
       </c>
       <c r="C25">
         <v>0.63</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>0.56700000000000006</v>
+      </c>
+      <c r="E25">
+        <f>1.2*C25</f>
+        <v>0.75600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2149,7 +2342,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5123F97E-0CC6-4065-B6E2-26F74ED855DA}">
   <sheetPr>
-    <tabColor theme="9" tint="0.39997558519241921"/>
+    <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2176,6 +2369,12 @@
       <c r="E1" t="s">
         <v>26</v>
       </c>
+      <c r="F1" s="11">
+        <v>0.85</v>
+      </c>
+      <c r="G1" s="11">
+        <v>1.1499999999999999</v>
+      </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
@@ -2193,6 +2392,14 @@
       <c r="E2">
         <v>7</v>
       </c>
+      <c r="F2">
+        <f>0.85*E2</f>
+        <v>5.95</v>
+      </c>
+      <c r="G2">
+        <f>1.15*E2</f>
+        <v>8.0499999999999989</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="15.75">
       <c r="A3">
@@ -2210,6 +2417,14 @@
       <c r="E3">
         <v>4.2</v>
       </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F16" si="0">0.85*E3</f>
+        <v>3.57</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G16" si="1">1.15*E3</f>
+        <v>4.83</v>
+      </c>
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:10">
@@ -2228,6 +2443,14 @@
       <c r="E4">
         <v>1.4</v>
       </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1.19</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>1.6099999999999999</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
@@ -2245,6 +2468,14 @@
       <c r="E5">
         <v>1.4</v>
       </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>1.19</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>1.6099999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
@@ -2262,6 +2493,14 @@
       <c r="E6">
         <v>7</v>
       </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>5.95</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>8.0499999999999989</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
@@ -2279,6 +2518,14 @@
       <c r="E7">
         <v>9</v>
       </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>7.6499999999999995</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>10.35</v>
+      </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
@@ -2296,6 +2543,14 @@
       <c r="E8">
         <v>5.4</v>
       </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>4.59</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>6.21</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
@@ -2313,6 +2568,14 @@
       <c r="E9">
         <v>1.8</v>
       </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>1.53</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>2.0699999999999998</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
@@ -2330,6 +2593,14 @@
       <c r="E10">
         <v>1.8</v>
       </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>1.53</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>2.0699999999999998</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
@@ -2347,6 +2618,14 @@
       <c r="E11">
         <v>9</v>
       </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>7.6499999999999995</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>10.35</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
@@ -2364,6 +2643,14 @@
       <c r="E12">
         <v>10</v>
       </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
@@ -2381,6 +2668,14 @@
       <c r="E13">
         <v>6</v>
       </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>6.8999999999999995</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
@@ -2398,6 +2693,14 @@
       <c r="E14">
         <v>2</v>
       </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>1.7</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>2.2999999999999998</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
@@ -2415,6 +2718,14 @@
       <c r="E15">
         <v>2</v>
       </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>1.7</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>2.2999999999999998</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
@@ -2431,6 +2742,14 @@
       </c>
       <c r="E16">
         <v>10</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>11.5</v>
       </c>
     </row>
     <row r="17" spans="2:2">
@@ -6418,13 +6737,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14629D0-DAA3-465E-A476-9A5F26F47902}">
   <sheetPr>
-    <tabColor theme="9" tint="0.39997558519241921"/>
+    <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6437,6 +6756,12 @@
       <c r="C1" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="D1" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="E1" s="11">
+        <v>1.2</v>
+      </c>
       <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:10">
@@ -6449,6 +6774,14 @@
       <c r="C2">
         <v>20571429</v>
       </c>
+      <c r="D2">
+        <f>C2*0.8</f>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E2">
+        <f>C2*1.2</f>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3">
@@ -6460,6 +6793,14 @@
       <c r="C3">
         <v>20571429</v>
       </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D37" si="0">C3*0.8</f>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E37" si="1">C3*1.2</f>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
@@ -6471,6 +6812,14 @@
       <c r="C4">
         <v>20571429</v>
       </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
@@ -6482,6 +6831,14 @@
       <c r="C5">
         <v>20571429</v>
       </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
@@ -6493,6 +6850,14 @@
       <c r="C6">
         <v>20571429</v>
       </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
@@ -6504,6 +6869,14 @@
       <c r="C7">
         <v>20571429</v>
       </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
@@ -6515,6 +6888,14 @@
       <c r="C8">
         <v>20571429</v>
       </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
@@ -6526,6 +6907,14 @@
       <c r="C9">
         <v>20571429</v>
       </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
@@ -6537,6 +6926,14 @@
       <c r="C10">
         <v>20571429</v>
       </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
@@ -6548,6 +6945,14 @@
       <c r="C11">
         <v>20571429</v>
       </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
@@ -6559,6 +6964,14 @@
       <c r="C12">
         <v>20571429</v>
       </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
@@ -6570,6 +6983,14 @@
       <c r="C13">
         <v>20571429</v>
       </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>16457143.200000001</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>24685714.800000001</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
@@ -6581,6 +7002,14 @@
       <c r="C14">
         <v>48214286</v>
       </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
@@ -6592,6 +7021,14 @@
       <c r="C15">
         <v>48214286</v>
       </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16">
@@ -6603,8 +7040,16 @@
       <c r="C16">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>2</v>
       </c>
@@ -6614,8 +7059,16 @@
       <c r="C17">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>2</v>
       </c>
@@ -6625,8 +7078,16 @@
       <c r="C18">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>2</v>
       </c>
@@ -6636,8 +7097,16 @@
       <c r="C19">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>2</v>
       </c>
@@ -6647,8 +7116,16 @@
       <c r="C20">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>2</v>
       </c>
@@ -6658,8 +7135,16 @@
       <c r="C21">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>2</v>
       </c>
@@ -6669,8 +7154,16 @@
       <c r="C22">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>2</v>
       </c>
@@ -6680,8 +7173,16 @@
       <c r="C23">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>2</v>
       </c>
@@ -6691,8 +7192,16 @@
       <c r="C24">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>2</v>
       </c>
@@ -6702,8 +7211,16 @@
       <c r="C25">
         <v>48214286</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>38571428.800000004</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="1"/>
+        <v>57857143.199999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>3</v>
       </c>
@@ -6713,8 +7230,16 @@
       <c r="C26">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>3</v>
       </c>
@@ -6724,8 +7249,16 @@
       <c r="C27">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>3</v>
       </c>
@@ -6735,8 +7268,16 @@
       <c r="C28">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>3</v>
       </c>
@@ -6746,8 +7287,16 @@
       <c r="C29">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>3</v>
       </c>
@@ -6757,8 +7306,16 @@
       <c r="C30">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>3</v>
       </c>
@@ -6768,8 +7325,16 @@
       <c r="C31">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>3</v>
       </c>
@@ -6779,8 +7344,16 @@
       <c r="C32">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>3</v>
       </c>
@@ -6790,8 +7363,16 @@
       <c r="C33">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>3</v>
       </c>
@@ -6801,8 +7382,16 @@
       <c r="C34">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>3</v>
       </c>
@@ -6812,8 +7401,16 @@
       <c r="C35">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>3</v>
       </c>
@@ -6823,8 +7420,16 @@
       <c r="C36">
         <v>21214286</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>3</v>
       </c>
@@ -6833,6 +7438,14 @@
       </c>
       <c r="C37">
         <v>21214286</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>16971428.800000001</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="1"/>
+        <v>25457143.199999999</v>
       </c>
     </row>
   </sheetData>
@@ -6845,42 +7458,71 @@
   <sheetPr>
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D1" s="11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="6">
+        <f>0.75*B2</f>
+        <v>13.5</v>
+      </c>
+      <c r="D2">
+        <f>0.5*B2</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="6">
+        <f t="shared" ref="C3:C4" si="0">0.75*B3</f>
+        <v>32.25</v>
+      </c>
+      <c r="D3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="9">
         <v>19</v>
+      </c>
+      <c r="C4" s="6">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
